--- a/output/pdf_financials_xlsx/UG.xlsx
+++ b/output/pdf_financials_xlsx/UG.xlsx
@@ -1645,10 +1645,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>3.8e-05</v>
+        <v>0.104719</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0.073614</v>
+        <v>0.178295</v>
       </c>
     </row>
     <row r="93">
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C103" s="3" t="n">
-        <v>0</v>
+        <v>-0.012855</v>
       </c>
     </row>
     <row r="104">
@@ -1834,7 +1834,7 @@
         <v>0.021705</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.219208</v>
+        <v>0.206353</v>
       </c>
     </row>
     <row r="107">
@@ -2446,7 +2446,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>-</t>
@@ -2670,7 +2674,11 @@
           <t>Warrants reserve (Note 8)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" s="5" t="n">
         <v>0.104681</v>
       </c>
@@ -2986,7 +2994,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/UG.xlsx
+++ b/output/pdf_financials_xlsx/UG.xlsx
@@ -553,10 +553,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.369062</v>
+        <v>0.381653</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.445333</v>
+        <v>1.09388</v>
       </c>
     </row>
     <row r="11">
@@ -566,10 +566,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.369062</v>
+        <v>-0.381653</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.445333</v>
+        <v>-1.09388</v>
       </c>
     </row>
     <row r="12">
@@ -878,7 +878,7 @@
         <v>0</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.84424</v>
       </c>
     </row>
     <row r="35">
@@ -904,7 +904,7 @@
         <v>0</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.84424</v>
       </c>
     </row>
     <row r="37">
@@ -1060,7 +1060,7 @@
         <v>0.795069</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.9021</v>
+        <v>0.05786</v>
       </c>
     </row>
     <row r="49">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E45" s="5" t="n">
